--- a/ti_specs.xlsx
+++ b/ti_specs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15039\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15039\applesauce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14E12000-5317-4381-A686-C6D7900C76FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577EBB90-A561-410E-AE0E-AD5DEA923DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="611">
   <si>
     <t/>
   </si>
@@ -1380,9 +1380,6 @@
   </si>
   <si>
     <t>Bi-directional</t>
-  </si>
-  <si>
-    <t>DFN2510</t>
   </si>
   <si>
     <t>ACTIVE</t>
@@ -9731,7 +9728,7 @@
         <v>448</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H172" s="3">
         <v>17</v>
@@ -9755,7 +9752,7 @@
         <v>10</v>
       </c>
       <c r="O172" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="173" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -9778,10 +9775,10 @@
         <v>1</v>
       </c>
       <c r="F173" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="G173" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="H173" s="3">
         <v>960</v>
@@ -9805,7 +9802,7 @@
         <v>6</v>
       </c>
       <c r="O173" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="174" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -9828,10 +9825,10 @@
         <v>1</v>
       </c>
       <c r="F174" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G174" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="H174" s="3">
         <v>1120</v>
@@ -9855,7 +9852,7 @@
         <v>6</v>
       </c>
       <c r="O174" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -9878,10 +9875,10 @@
         <v>1</v>
       </c>
       <c r="F175" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G175" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="H175" s="3">
         <v>1250</v>
@@ -9905,7 +9902,7 @@
         <v>6</v>
       </c>
       <c r="O175" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -9928,10 +9925,10 @@
         <v>1</v>
       </c>
       <c r="F176" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G176" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="H176" s="3">
         <v>820</v>
@@ -9955,7 +9952,7 @@
         <v>6</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="177" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -9978,10 +9975,10 @@
         <v>1</v>
       </c>
       <c r="F177" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G177" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="H177" s="3">
         <v>400</v>
@@ -10005,7 +10002,7 @@
         <v>6</v>
       </c>
       <c r="O177" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10028,10 +10025,10 @@
         <v>4</v>
       </c>
       <c r="F178" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="H178" s="3">
         <v>17</v>
@@ -10055,7 +10052,7 @@
         <v>10</v>
       </c>
       <c r="O178" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10078,10 +10075,10 @@
         <v>1</v>
       </c>
       <c r="F179" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="G179" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="H179" s="3">
         <v>67</v>
@@ -10105,7 +10102,7 @@
         <v>2</v>
       </c>
       <c r="O179" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="180" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10128,10 +10125,10 @@
         <v>2</v>
       </c>
       <c r="F180" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="G180" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="H180" s="3">
         <v>20</v>
@@ -10155,7 +10152,7 @@
         <v>3</v>
       </c>
       <c r="O180" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="181" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10178,10 +10175,10 @@
         <v>1</v>
       </c>
       <c r="F181" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G181" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="H181" s="3">
         <v>1330</v>
@@ -10202,10 +10199,10 @@
         <v>0.216</v>
       </c>
       <c r="N181" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="O181" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="O181" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="182" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10228,10 +10225,10 @@
         <v>1</v>
       </c>
       <c r="F182" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G182" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="H182" s="3">
         <v>30</v>
@@ -10246,7 +10243,7 @@
         <v>2.5</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M182" s="3">
         <v>9.2999999999999999E-2</v>
@@ -10255,7 +10252,7 @@
         <v>2</v>
       </c>
       <c r="O182" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10278,10 +10275,10 @@
         <v>1</v>
       </c>
       <c r="F183" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="G183" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="H183" s="3">
         <v>90</v>
@@ -10305,7 +10302,7 @@
         <v>2</v>
       </c>
       <c r="O183" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10328,10 +10325,10 @@
         <v>1</v>
       </c>
       <c r="F184" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="G184" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="H184" s="3">
         <v>90</v>
@@ -10355,7 +10352,7 @@
         <v>2</v>
       </c>
       <c r="O184" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="185" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10378,10 +10375,10 @@
         <v>1</v>
       </c>
       <c r="F185" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G185" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="H185" s="3">
         <v>50</v>
@@ -10405,7 +10402,7 @@
         <v>2</v>
       </c>
       <c r="O185" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="186" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10428,10 +10425,10 @@
         <v>1</v>
       </c>
       <c r="F186" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="G186" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="H186" s="3">
         <v>15</v>
@@ -10455,7 +10452,7 @@
         <v>2</v>
       </c>
       <c r="O186" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="187" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10478,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="F187" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="G187" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="H187" s="3">
         <v>27</v>
@@ -10505,7 +10502,7 @@
         <v>2</v>
       </c>
       <c r="O187" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="188" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10528,10 +10525,10 @@
         <v>1</v>
       </c>
       <c r="F188" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="G188" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="H188" s="3">
         <v>19</v>
@@ -10555,7 +10552,7 @@
         <v>2</v>
       </c>
       <c r="O188" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="189" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10578,10 +10575,10 @@
         <v>4</v>
       </c>
       <c r="F189" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="G189" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="H189" s="3">
         <v>17</v>
@@ -10605,7 +10602,7 @@
         <v>10</v>
       </c>
       <c r="O189" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10628,10 +10625,10 @@
         <v>2</v>
       </c>
       <c r="F190" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G190" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>505</v>
       </c>
       <c r="H190" s="3">
         <v>75</v>
@@ -10655,7 +10652,7 @@
         <v>3</v>
       </c>
       <c r="O190" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10678,10 +10675,10 @@
         <v>4</v>
       </c>
       <c r="F191" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="G191" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="H191" s="3">
         <v>40</v>
@@ -10705,7 +10702,7 @@
         <v>10</v>
       </c>
       <c r="O191" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="192" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10728,10 +10725,10 @@
         <v>4</v>
       </c>
       <c r="F192" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="G192" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="H192" s="3">
         <v>40</v>
@@ -10755,7 +10752,7 @@
         <v>4</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10778,10 +10775,10 @@
         <v>4</v>
       </c>
       <c r="F193" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G193" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="H193" s="3">
         <v>35</v>
@@ -10805,7 +10802,7 @@
         <v>4</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="194" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10828,10 +10825,10 @@
         <v>2</v>
       </c>
       <c r="F194" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G194" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="H194" s="3">
         <v>35</v>
@@ -10855,7 +10852,7 @@
         <v>6</v>
       </c>
       <c r="O194" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="195" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10878,10 +10875,10 @@
         <v>6</v>
       </c>
       <c r="F195" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G195" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="H195" s="3">
         <v>40</v>
@@ -10905,7 +10902,7 @@
         <v>14</v>
       </c>
       <c r="O195" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="196" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10928,10 +10925,10 @@
         <v>2</v>
       </c>
       <c r="F196" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="G196" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="H196" s="3">
         <v>85</v>
@@ -10952,10 +10949,10 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="N196" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="O196" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="O196" s="3" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -10978,10 +10975,10 @@
         <v>4</v>
       </c>
       <c r="F197" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G197" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>527</v>
       </c>
       <c r="H197" s="3">
         <v>100</v>
@@ -11005,7 +11002,7 @@
         <v>6</v>
       </c>
       <c r="O197" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11028,10 +11025,10 @@
         <v>4</v>
       </c>
       <c r="F198" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G198" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>530</v>
       </c>
       <c r="H198" s="3">
         <v>40</v>
@@ -11055,7 +11052,7 @@
         <v>10</v>
       </c>
       <c r="O198" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="199" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11078,10 +11075,10 @@
         <v>1</v>
       </c>
       <c r="F199" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G199" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="H199" s="3">
         <v>40</v>
@@ -11105,7 +11102,7 @@
         <v>2</v>
       </c>
       <c r="O199" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="200" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11128,10 +11125,10 @@
         <v>4</v>
       </c>
       <c r="F200" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G200" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="H200" s="3">
         <v>45</v>
@@ -11155,7 +11152,7 @@
         <v>6</v>
       </c>
       <c r="O200" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="201" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11178,10 +11175,10 @@
         <v>4</v>
       </c>
       <c r="F201" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="G201" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>539</v>
       </c>
       <c r="H201" s="3">
         <v>45</v>
@@ -11205,7 +11202,7 @@
         <v>6</v>
       </c>
       <c r="O201" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="202" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11228,7 +11225,7 @@
         <v>5</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="3">
@@ -11253,7 +11250,7 @@
         <v>6</v>
       </c>
       <c r="O202" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="203" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11276,10 +11273,10 @@
         <v>1</v>
       </c>
       <c r="F203" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="G203" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="H203" s="3">
         <v>50</v>
@@ -11303,7 +11300,7 @@
         <v>2</v>
       </c>
       <c r="O203" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="204" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11326,10 +11323,10 @@
         <v>4</v>
       </c>
       <c r="F204" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="G204" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="H204" s="3">
         <v>40</v>
@@ -11353,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11376,10 +11373,10 @@
         <v>1</v>
       </c>
       <c r="F205" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G205" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>550</v>
       </c>
       <c r="H205" s="3">
         <v>90</v>
@@ -11403,7 +11400,7 @@
         <v>2</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="206" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11426,10 +11423,10 @@
         <v>1</v>
       </c>
       <c r="F206" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G206" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="H206" s="3">
         <v>90</v>
@@ -11453,7 +11450,7 @@
         <v>2</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="207" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11476,10 +11473,10 @@
         <v>2</v>
       </c>
       <c r="F207" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G207" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="G207" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="H207" s="3">
         <v>45</v>
@@ -11503,7 +11500,7 @@
         <v>3</v>
       </c>
       <c r="O207" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="208" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11526,10 +11523,10 @@
         <v>4</v>
       </c>
       <c r="F208" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G208" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="G208" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="H208" s="3">
         <v>45</v>
@@ -11553,7 +11550,7 @@
         <v>10</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="209" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11576,10 +11573,10 @@
         <v>2</v>
       </c>
       <c r="F209" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G209" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="G209" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="H209" s="3">
         <v>45</v>
@@ -11603,7 +11600,7 @@
         <v>3</v>
       </c>
       <c r="O209" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="210" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11619,16 +11616,16 @@
         <v>PDF datasheet</v>
       </c>
       <c r="D210" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E210" s="3">
+        <v>2</v>
+      </c>
+      <c r="F210" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E210" s="3">
-        <v>2</v>
-      </c>
-      <c r="F210" s="3" t="s">
+      <c r="G210" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="G210" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="H210" s="3">
         <v>100</v>
@@ -11650,7 +11647,7 @@
         <v>5</v>
       </c>
       <c r="O210" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11673,10 +11670,10 @@
         <v>2</v>
       </c>
       <c r="F211" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="G211" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="H211" s="3"/>
       <c r="I211" s="3">
@@ -11698,7 +11695,7 @@
         <v>6</v>
       </c>
       <c r="O211" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11721,10 +11718,10 @@
         <v>2</v>
       </c>
       <c r="F212" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="G212" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="H212" s="3">
         <v>45</v>
@@ -11748,7 +11745,7 @@
         <v>3</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="213" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11771,10 +11768,10 @@
         <v>2</v>
       </c>
       <c r="F213" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="G213" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="H213" s="3">
         <v>0.27</v>
@@ -11795,10 +11792,10 @@
         <v>0.29399999999999998</v>
       </c>
       <c r="N213" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="O213" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="O213" s="3" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="214" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11821,10 +11818,10 @@
         <v>4</v>
       </c>
       <c r="F214" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="G214" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="H214" s="3">
         <v>25</v>
@@ -11848,7 +11845,7 @@
         <v>10</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="215" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11871,10 +11868,10 @@
         <v>4</v>
       </c>
       <c r="F215" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G215" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>582</v>
       </c>
       <c r="H215" s="3">
         <v>60</v>
@@ -11898,7 +11895,7 @@
         <v>6</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="216" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11921,10 +11918,10 @@
         <v>8</v>
       </c>
       <c r="F216" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G216" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="H216" s="3">
         <v>25</v>
@@ -11948,7 +11945,7 @@
         <v>15</v>
       </c>
       <c r="O216" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="217" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -11971,10 +11968,10 @@
         <v>4</v>
       </c>
       <c r="F217" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="G217" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="H217" s="3">
         <v>25</v>
@@ -11995,10 +11992,10 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="N217" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="O217" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="O217" s="3" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12021,10 +12018,10 @@
         <v>2</v>
       </c>
       <c r="F218" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="G218" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="G218" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="H218" s="3">
         <v>100</v>
@@ -12043,10 +12040,10 @@
         <v>0.121</v>
       </c>
       <c r="N218" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="O218" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="O218" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="219" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12069,10 +12066,10 @@
         <v>3</v>
       </c>
       <c r="F219" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="G219" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>596</v>
       </c>
       <c r="H219" s="3">
         <v>100</v>
@@ -12093,10 +12090,10 @@
         <v>0.155</v>
       </c>
       <c r="N219" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O219" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="O219" s="3" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="220" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12119,10 +12116,10 @@
         <v>4</v>
       </c>
       <c r="F220" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="G220" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="H220" s="3">
         <v>25</v>
@@ -12146,7 +12143,7 @@
         <v>5</v>
       </c>
       <c r="O220" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="221" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12169,10 +12166,10 @@
         <v>4</v>
       </c>
       <c r="F221" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="G221" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>603</v>
       </c>
       <c r="H221" s="3">
         <v>100</v>
@@ -12196,7 +12193,7 @@
         <v>6</v>
       </c>
       <c r="O221" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="222" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12219,10 +12216,10 @@
         <v>6</v>
       </c>
       <c r="F222" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="G222" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="H222" s="3">
         <v>100</v>
@@ -12241,10 +12238,10 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="N222" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="O222" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="O222" s="3" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="223" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -12258,12 +12255,12 @@
         <v>PDF datasheet</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
@@ -12274,10 +12271,10 @@
         <v>204.517</v>
       </c>
       <c r="N223" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="O223" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="O223" s="3" t="s">
-        <v>611</v>
       </c>
     </row>
   </sheetData>
